--- a/tests/data/full_example/output/excel/full_example.xlsx
+++ b/tests/data/full_example/output/excel/full_example.xlsx
@@ -18778,32 +18778,32 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>protein:Beef_protein_beef</t>
+          <t>protein:Beef_beef_protein</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>protein:Beef_protein_milk</t>
+          <t>protein:Beef_milk_protein</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>protein:Dairy_protein_beef</t>
+          <t>protein:Dairy_beef_protein</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>protein:Dairy_protein_milk</t>
+          <t>protein:Dairy_milk_protein</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>protein:Spared Cattle/Sheep area_protein_beef</t>
+          <t>protein:Spared Cattle/Sheep area_beef_protein</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>protein:Spared Cattle/Sheep area_protein_milk</t>
+          <t>protein:Spared Cattle/Sheep area_milk_protein</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -18892,16 +18892,16 @@
         <v>24.649</v>
       </c>
       <c r="AA2" t="n">
-        <v>286692610.1</v>
+        <v>65939.30032299999</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>366122762.33</v>
+        <v>84208.2353359</v>
       </c>
       <c r="AD2" t="n">
-        <v>8194875975</v>
+        <v>286820.659125</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -18910,7 +18910,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>8847691347.43</v>
+        <v>436968.1947839</v>
       </c>
     </row>
     <row r="3">
@@ -18993,16 +18993,16 @@
         <v>24.38194579409902</v>
       </c>
       <c r="AA3" t="n">
-        <v>282083141.5876399</v>
+        <v>64879.12256515717</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>363366246.0178301</v>
+        <v>83574.23658410092</v>
       </c>
       <c r="AD3" t="n">
-        <v>8133177245.433068</v>
+        <v>284661.2035901574</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -19011,7 +19011,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>8778626633.038538</v>
+        <v>433114.5627394155</v>
       </c>
     </row>
     <row r="4">
@@ -19094,16 +19094,16 @@
         <v>24.11505131119322</v>
       </c>
       <c r="AA4" t="n">
-        <v>277524125.3024577</v>
+        <v>63830.54881956527</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>360572985.004957</v>
+        <v>82931.7865511401</v>
       </c>
       <c r="AD4" t="n">
-        <v>8070656064.229736</v>
+        <v>282472.9622480408</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -19112,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>8708753174.537151</v>
+        <v>429235.2976187461</v>
       </c>
     </row>
     <row r="5">
@@ -19195,16 +19195,16 @@
         <v>23.84831394322052</v>
       </c>
       <c r="AA5" t="n">
-        <v>273014737.4273199</v>
+        <v>62793.38960828358</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>357743579.2830102</v>
+        <v>82281.02323509235</v>
       </c>
       <c r="AD5" t="n">
-        <v>8007325860.921016</v>
+        <v>280256.4051322356</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -19213,7 +19213,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>8638084177.631346</v>
+        <v>425330.8179756115</v>
       </c>
     </row>
     <row r="6">
@@ -19296,16 +19296,16 @@
         <v>23.58173113859303</v>
       </c>
       <c r="AA6" t="n">
-        <v>268554171.9837698</v>
+        <v>61767.45955626707</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>354878615.8515897</v>
+        <v>81622.08164586565</v>
       </c>
       <c r="AD6" t="n">
-        <v>7943199774.239087</v>
+        <v>278011.9920983681</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -19314,7 +19314,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>8566632562.074447</v>
+        <v>421401.5333005008</v>
       </c>
     </row>
     <row r="7">
@@ -19397,16 +19397,16 @@
         <v>23.31530040067661</v>
       </c>
       <c r="AA7" t="n">
-        <v>264141640.3517852</v>
+        <v>60752.57728091061</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>351978669.0680295</v>
+        <v>80955.09388564677</v>
       </c>
       <c r="AD7" t="n">
-        <v>7878290659.946006</v>
+        <v>275740.1730981102</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -19415,7 +19415,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>8494410969.365821</v>
+        <v>417447.8442646677</v>
       </c>
     </row>
     <row r="8">
@@ -19498,16 +19498,16 @@
         <v>23.04901928631942</v>
       </c>
       <c r="AA8" t="n">
-        <v>259776370.8049688</v>
+        <v>59748.56528514283</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>349044300.9859208</v>
+        <v>80280.18922676181</v>
       </c>
       <c r="AD8" t="n">
-        <v>7812611098.410838</v>
+        <v>273441.3884443794</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -19516,7 +19516,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>8421431770.201728</v>
+        <v>413470.142956284</v>
       </c>
     </row>
     <row r="9">
@@ -19599,16 +19599,16 @@
         <v>22.78288540442743</v>
       </c>
       <c r="AA9" t="n">
-        <v>255457608.0605937</v>
+        <v>58755.24985393655</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>346076061.6828186</v>
+        <v>79597.49418704829</v>
       </c>
       <c r="AD9" t="n">
-        <v>7746173401.944649</v>
+        <v>271116.0690680627</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -19617,7 +19617,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>8347707071.688061</v>
+        <v>409468.8131090475</v>
       </c>
     </row>
     <row r="10">
@@ -19700,16 +19700,16 @@
         <v>22.51689641458522</v>
       </c>
       <c r="AA10" t="n">
-        <v>251184612.8439542</v>
+        <v>57772.46095410948</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>343074489.5775261</v>
+        <v>78907.132602831</v>
       </c>
       <c r="AD10" t="n">
-        <v>7678989621.902257</v>
+        <v>268764.6367665791</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -19718,7 +19718,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>8273248724.323737</v>
+        <v>405444.2303235196</v>
       </c>
     </row>
     <row r="11">
@@ -19801,16 +19801,16 @@
         <v>22.25105002572042</v>
       </c>
       <c r="AA11" t="n">
-        <v>246956661.4664946</v>
+        <v>56800.03213729375</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>340040111.7373481</v>
+        <v>78209.22569959007</v>
       </c>
       <c r="AD11" t="n">
-        <v>7611071555.559434</v>
+        <v>266387.5044445802</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -19819,7 +19819,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>8198068328.763277</v>
+        <v>401396.7622814641</v>
       </c>
     </row>
     <row r="12">
@@ -19902,16 +19902,16 @@
         <v>21.98534399481016</v>
       </c>
       <c r="AA12" t="n">
-        <v>242773045.4172074</v>
+        <v>55837.80044595771</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>336973444.1756771</v>
+        <v>77503.89216040573</v>
       </c>
       <c r="AD12" t="n">
-        <v>7542430752.773731</v>
+        <v>263985.0763470806</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -19920,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>8122177242.366616</v>
+        <v>397326.7689534441</v>
       </c>
     </row>
     <row r="13">
@@ -20003,16 +20003,16 @@
         <v>18.34410062912544</v>
       </c>
       <c r="AA13" t="n">
-        <v>236185373.5745325</v>
+        <v>54322.63592214248</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>330450383.2027825</v>
+        <v>76003.58813663997</v>
       </c>
       <c r="AD13" t="n">
-        <v>7796819158.859326</v>
+        <v>272888.6705600765</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -20021,7 +20021,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>8363454915.636642</v>
+        <v>403214.8946188589</v>
       </c>
     </row>
     <row r="14">
@@ -20104,16 +20104,16 @@
         <v>17.73224987661764</v>
       </c>
       <c r="AA14" t="n">
-        <v>230769778.992563</v>
+        <v>53077.04916828951</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>325434002.4794097</v>
+        <v>74849.82057026423</v>
       </c>
       <c r="AD14" t="n">
-        <v>7714306871.289419</v>
+        <v>270000.7404951297</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -20122,7 +20122,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>8270510652.761393</v>
+        <v>397927.6102336835</v>
       </c>
     </row>
     <row r="15">
@@ -20205,16 +20205,16 @@
         <v>17.13111923368567</v>
       </c>
       <c r="AA15" t="n">
-        <v>225413373.388051</v>
+        <v>51845.07587925172</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>320381562.9460251</v>
+        <v>73687.75947758577</v>
       </c>
       <c r="AD15" t="n">
-        <v>7629830732.569513</v>
+        <v>267044.075639933</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -20223,7 +20223,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>8175625668.903589</v>
+        <v>392576.9109967705</v>
       </c>
     </row>
     <row r="16">
@@ -20306,16 +20306,16 @@
         <v>16.54069065275236</v>
       </c>
       <c r="AA16" t="n">
-        <v>220115290.6457102</v>
+        <v>50626.51684851334</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>315293794.285962</v>
+        <v>72517.57268577127</v>
       </c>
       <c r="AD16" t="n">
-        <v>7543396284.632818</v>
+        <v>264018.8699621487</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>8078805369.56449</v>
+        <v>387162.9594964333</v>
       </c>
     </row>
     <row r="17">
@@ -20407,16 +20407,16 @@
         <v>15.96094597217893</v>
       </c>
       <c r="AA17" t="n">
-        <v>214874681.1749404</v>
+        <v>49421.17667023629</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>310171411.5937402</v>
+        <v>71339.42466656024</v>
       </c>
       <c r="AD17" t="n">
-        <v>7455009040.269443</v>
+        <v>260925.3164094305</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -20425,7 +20425,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>7980055133.038123</v>
+        <v>381685.917746227</v>
       </c>
     </row>
     <row r="18">
@@ -20508,16 +20508,16 @@
         <v>15.39186692088821</v>
       </c>
       <c r="AA18" t="n">
-        <v>209690711.5188011</v>
+        <v>48228.86364932424</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>305015115.723083</v>
+        <v>70153.47661630908</v>
       </c>
       <c r="AD18" t="n">
-        <v>7364674483.494518</v>
+        <v>257763.6069223082</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -20526,7 +20526,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>7879380310.736402</v>
+        <v>376145.9471879415</v>
       </c>
     </row>
     <row r="19">
@@ -20609,16 +20609,16 @@
         <v>14.83343512284735</v>
       </c>
       <c r="AA19" t="n">
-        <v>204562563.9740304</v>
+        <v>47049.38971402699</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>299825593.6250904</v>
+        <v>68959.88653377078</v>
       </c>
       <c r="AD19" t="n">
-        <v>7272398069.907548</v>
+        <v>254533.9324467642</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -20627,7 +20627,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>7776786227.506669</v>
+        <v>370543.208694562</v>
       </c>
     </row>
     <row r="20">
@@ -20710,16 +20710,16 @@
         <v>14.28563210141512</v>
       </c>
       <c r="AA20" t="n">
-        <v>199489436.2217476</v>
+        <v>45882.57033100195</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>294603518.6768909</v>
+        <v>67758.8092956849</v>
       </c>
       <c r="AD20" t="n">
-        <v>7178185227.043273</v>
+        <v>251236.4829465146</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -20728,7 +20728,7 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>7672278181.941911</v>
+        <v>364877.8625732014</v>
       </c>
     </row>
     <row r="21">
@@ -20811,16 +20811,16 @@
         <v>13.74843928355786</v>
       </c>
       <c r="AA21" t="n">
-        <v>194470540.9684891</v>
+        <v>44728.22442275249</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>289349551.0010814</v>
+        <v>66550.39673024873</v>
       </c>
       <c r="AD21" t="n">
-        <v>7082041354.714284</v>
+        <v>247871.447415</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -20829,7 +20829,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>7565861446.683854</v>
+        <v>359150.0685680012</v>
       </c>
     </row>
     <row r="22">
@@ -20912,16 +20912,16 @@
         <v>13.22183800393869</v>
       </c>
       <c r="AA22" t="n">
-        <v>189505105.5972433</v>
+        <v>43586.17428736596</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>284064337.7762576</v>
+        <v>65334.79768853926</v>
       </c>
       <c r="AD22" t="n">
-        <v>6983971825.345688</v>
+        <v>244439.0138870991</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>7457541268.719189</v>
+        <v>353359.9858630043</v>
       </c>
     </row>
     <row r="23">
@@ -21013,16 +21013,16 @@
         <v>5.997581800986327</v>
       </c>
       <c r="AA23" t="n">
-        <v>209121570.5577907</v>
+        <v>48097.96122829187</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>315789468.2461405</v>
+        <v>72631.57769661231</v>
       </c>
       <c r="AD23" t="n">
-        <v>8529220412.249276</v>
+        <v>298522.7144287247</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -21031,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>9054131451.053207</v>
+        <v>419252.2533536289</v>
       </c>
     </row>
     <row r="24">
@@ -21114,16 +21114,16 @@
         <v>5.207249407903465</v>
       </c>
       <c r="AA24" t="n">
-        <v>203285746.1542771</v>
+        <v>46755.72161548373</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>309232619.0444865</v>
+        <v>71123.50238023189</v>
       </c>
       <c r="AD24" t="n">
-        <v>8420249624.981268</v>
+        <v>294708.7368743444</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -21132,7 +21132,7 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>8932767990.180033</v>
+        <v>412587.96087006</v>
       </c>
     </row>
     <row r="25">
@@ -21215,16 +21215,16 @@
         <v>4.446575499619509</v>
       </c>
       <c r="AA25" t="n">
-        <v>197446492.6364355</v>
+        <v>45412.69330638018</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>302541005.1459399</v>
+        <v>69584.43118356618</v>
       </c>
       <c r="AD25" t="n">
-        <v>8304690604.204634</v>
+        <v>290664.1711471622</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -21233,7 +21233,7 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>8804678101.987011</v>
+        <v>405661.2956371086</v>
       </c>
     </row>
     <row r="26">
@@ -21316,16 +21316,16 @@
         <v>3.716108589958206</v>
       </c>
       <c r="AA26" t="n">
-        <v>191602858.6404746</v>
+        <v>44068.65748730916</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>295713044.0995206</v>
+        <v>68014.00014288974</v>
       </c>
       <c r="AD26" t="n">
-        <v>8182410496.684883</v>
+        <v>286384.3673839709</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -21334,7 +21334,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>8669726399.424879</v>
+        <v>398467.0250141699</v>
       </c>
     </row>
     <row r="27">
@@ -21417,16 +21417,16 @@
         <v>3.016409729517187</v>
       </c>
       <c r="AA27" t="n">
-        <v>185753886.5118971</v>
+        <v>42723.39389773633</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>288747101.4496902</v>
+        <v>66411.83333342875</v>
       </c>
       <c r="AD27" t="n">
-        <v>8053273604.293139</v>
+        <v>281864.5761502599</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -21435,7 +21435,7 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>8527774592.254725</v>
+        <v>390999.803381425</v>
       </c>
     </row>
     <row r="28">
@@ -21518,16 +21518,16 @@
         <v>2.346787897598084</v>
       </c>
       <c r="AA28" t="n">
-        <v>179801693.0449991</v>
+        <v>41354.38940034981</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>281489757.78293</v>
+        <v>64742.64429007391</v>
       </c>
       <c r="AD28" t="n">
-        <v>7912876006.179801</v>
+        <v>276950.6602162931</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -21536,7 +21536,7 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>8374167457.00773</v>
+        <v>383047.6939067168</v>
       </c>
     </row>
     <row r="29">
@@ -21619,16 +21619,16 @@
         <v>1.709716177140871</v>
       </c>
       <c r="AA29" t="n">
-        <v>173841939.2020508</v>
+        <v>39983.64601647168</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>274088401.1562204</v>
+        <v>63040.33226593069</v>
       </c>
       <c r="AD29" t="n">
-        <v>7765200766.241389</v>
+        <v>271782.0268184487</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -21637,7 +21637,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>8213131106.599661</v>
+        <v>374806.0051008511</v>
       </c>
     </row>
     <row r="30">
@@ -21720,16 +21720,16 @@
         <v>1.105807140242641</v>
       </c>
       <c r="AA30" t="n">
-        <v>167873628.1021593</v>
+        <v>38610.93446349664</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>266541197.0996344</v>
+        <v>61304.47533291591</v>
       </c>
       <c r="AD30" t="n">
-        <v>7610100329.083528</v>
+        <v>266353.5115179235</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -21738,7 +21738,7 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>8044515154.285321</v>
+        <v>366268.921314336</v>
       </c>
     </row>
     <row r="31">
@@ -21821,16 +21821,16 @@
         <v>0.5356877879524105</v>
       </c>
       <c r="AA31" t="n">
-        <v>161895754.087623</v>
+        <v>37236.0234401533</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>258846252.8643243</v>
+        <v>59534.63815879458</v>
       </c>
       <c r="AD31" t="n">
-        <v>7447423845.986404</v>
+        <v>260659.8346095242</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -21839,7 +21839,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>7868165852.938352</v>
+        <v>357430.4962084721</v>
       </c>
     </row>
     <row r="32">
@@ -21922,16 +21922,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD32" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -21940,7 +21940,7 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="33">
@@ -22023,16 +22023,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD33" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -22041,7 +22041,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="34">
@@ -22124,16 +22124,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD34" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -22142,7 +22142,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="35">
@@ -22225,16 +22225,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD35" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -22243,7 +22243,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="36">
@@ -22326,16 +22326,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD36" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -22344,7 +22344,7 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="37">
@@ -22427,16 +22427,16 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD37" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -22445,7 +22445,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="38">
@@ -22528,16 +22528,16 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD38" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -22546,7 +22546,7 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="39">
@@ -22629,16 +22629,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD39" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -22647,7 +22647,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="40">
@@ -22730,16 +22730,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD40" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -22748,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="41">
@@ -22831,16 +22831,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD41" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -22849,7 +22849,7 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="42">
@@ -22932,16 +22932,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD42" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="43">
@@ -23033,16 +23033,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD43" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -23051,7 +23051,7 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="44">
@@ -23134,16 +23134,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD44" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -23152,7 +23152,7 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="45">
@@ -23235,16 +23235,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD45" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -23253,7 +23253,7 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="46">
@@ -23336,16 +23336,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD46" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -23354,7 +23354,7 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="47">
@@ -23437,16 +23437,16 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD47" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="48">
@@ -23538,16 +23538,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD48" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -23556,7 +23556,7 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="49">
@@ -23639,16 +23639,16 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD49" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="50">
@@ -23740,16 +23740,16 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD50" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -23758,7 +23758,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="51">
@@ -23841,16 +23841,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD51" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="52">
@@ -23942,16 +23942,16 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD52" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="53">
@@ -24043,16 +24043,16 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD53" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -24061,7 +24061,7 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="54">
@@ -24144,16 +24144,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD54" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="55">
@@ -24245,16 +24245,16 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD55" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -24263,7 +24263,7 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="56">
@@ -24346,16 +24346,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD56" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -24364,7 +24364,7 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="57">
@@ -24447,16 +24447,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD57" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="58">
@@ -24548,16 +24548,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD58" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -24566,7 +24566,7 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="59">
@@ -24649,16 +24649,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD59" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -24667,7 +24667,7 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="60">
@@ -24750,16 +24750,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD60" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -24768,7 +24768,7 @@
         <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="61">
@@ -24851,16 +24851,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD61" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -24869,7 +24869,7 @@
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="62">
@@ -24952,16 +24952,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD62" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="63">
@@ -25053,16 +25053,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD63" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -25071,7 +25071,7 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="64">
@@ -25154,16 +25154,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD64" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -25172,7 +25172,7 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="65">
@@ -25255,16 +25255,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD65" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -25273,7 +25273,7 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="66">
@@ -25356,16 +25356,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD66" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="67">
@@ -25457,16 +25457,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB67" t="n">
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD67" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="68">
@@ -25558,16 +25558,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB68" t="n">
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD68" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -25576,7 +25576,7 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="69">
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB69" t="n">
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD69" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -25677,7 +25677,7 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="70">
@@ -25760,16 +25760,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB70" t="n">
         <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD70" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -25778,7 +25778,7 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="71">
@@ -25861,16 +25861,16 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD71" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -25879,7 +25879,7 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="72">
@@ -25962,16 +25962,16 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD72" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -25980,7 +25980,7 @@
         <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="73">
@@ -26063,16 +26063,16 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD73" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE73" t="n">
         <v>0</v>
@@ -26081,7 +26081,7 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="74">
@@ -26164,16 +26164,16 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD74" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -26182,7 +26182,7 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="75">
@@ -26265,16 +26265,16 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD75" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE75" t="n">
         <v>0</v>
@@ -26283,7 +26283,7 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="76">
@@ -26366,16 +26366,16 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD76" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE76" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="77">
@@ -26467,16 +26467,16 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD77" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE77" t="n">
         <v>0</v>
@@ -26485,7 +26485,7 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="78">
@@ -26568,16 +26568,16 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD78" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE78" t="n">
         <v>0</v>
@@ -26586,7 +26586,7 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="79">
@@ -26669,16 +26669,16 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD79" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE79" t="n">
         <v>0</v>
@@ -26687,7 +26687,7 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="80">
@@ -26770,16 +26770,16 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD80" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="81">
@@ -26871,16 +26871,16 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB81" t="n">
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD81" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -26889,7 +26889,7 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
     <row r="82">
@@ -26972,16 +26972,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>155907302.1129118</v>
+        <v>35858.67948596972</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>251001615.9518708</v>
+        <v>57730.37166893027</v>
       </c>
       <c r="AD82" t="n">
-        <v>7277017068.073106</v>
+        <v>254695.5973825587</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -26990,7 +26990,7 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>7683925986.137889</v>
+        <v>348284.6485374587</v>
       </c>
     </row>
   </sheetData>
@@ -27277,7 +27277,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB2" t="n">
-        <v>444.5474675700861</v>
+        <v>444.5474675700862</v>
       </c>
       <c r="AC2" t="n">
         <v>1287.167022565553</v>
@@ -27295,7 +27295,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -27390,7 +27390,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.5474675700861</v>
+        <v>444.5474675700862</v>
       </c>
       <c r="AC3" t="n">
         <v>1287.167022565553</v>
@@ -27408,7 +27408,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -27503,7 +27503,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB4" t="n">
-        <v>444.5474675700861</v>
+        <v>444.5474675700862</v>
       </c>
       <c r="AC4" t="n">
         <v>1287.167022565553</v>
@@ -27521,7 +27521,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -27616,7 +27616,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB5" t="n">
-        <v>444.5474675700861</v>
+        <v>444.5474675700862</v>
       </c>
       <c r="AC5" t="n">
         <v>1287.167022565553</v>
@@ -27634,7 +27634,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -27747,7 +27747,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -27860,7 +27860,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB8" t="n">
-        <v>443.4124527592688</v>
+        <v>443.4124527592689</v>
       </c>
       <c r="AC8" t="n">
         <v>1287.167022565553</v>
@@ -27973,7 +27973,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -28068,7 +28068,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB9" t="n">
-        <v>441.8990996781792</v>
+        <v>441.8990996781793</v>
       </c>
       <c r="AC9" t="n">
         <v>1287.167022565553</v>
@@ -28086,7 +28086,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -28199,7 +28199,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -28312,7 +28312,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -28407,7 +28407,7 @@
         <v>844.5843507142857</v>
       </c>
       <c r="AB12" t="n">
-        <v>437.3590404349102</v>
+        <v>437.3590404349103</v>
       </c>
       <c r="AC12" t="n">
         <v>1287.167022565553</v>
@@ -28425,7 +28425,7 @@
         <v>0.039567</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01939928571428572</v>
+        <v>0.01939928571428571</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -28493,10 +28493,10 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S13" t="n">
-        <v>45.98283458124946</v>
+        <v>45.98283458124945</v>
       </c>
       <c r="T13" t="n">
-        <v>133.2314981323934</v>
+        <v>133.2314981323933</v>
       </c>
       <c r="U13" t="n">
         <v>781.4163243333333</v>
@@ -28508,7 +28508,7 @@
         <v>-518.8620467864769</v>
       </c>
       <c r="X13" t="n">
-        <v>501.1675839229207</v>
+        <v>501.1675839229206</v>
       </c>
       <c r="Y13" t="n">
         <v>1733.350842303111</v>
@@ -28520,7 +28520,7 @@
         <v>831.9155854535715</v>
       </c>
       <c r="AB13" t="n">
-        <v>426.1034768943059</v>
+        <v>426.103476894306</v>
       </c>
       <c r="AC13" t="n">
         <v>1287.167022565553</v>
@@ -28547,7 +28547,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.05808179142857143</v>
+        <v>0.05808179142857142</v>
       </c>
     </row>
     <row r="14">
@@ -28606,7 +28606,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S14" t="n">
-        <v>46.28604042857687</v>
+        <v>46.28604042857686</v>
       </c>
       <c r="T14" t="n">
         <v>133.8776733397208</v>
@@ -28633,7 +28633,7 @@
         <v>819.2468201928572</v>
       </c>
       <c r="AB14" t="n">
-        <v>414.8479133537016</v>
+        <v>414.8479133537017</v>
       </c>
       <c r="AC14" t="n">
         <v>1287.167022565553</v>
@@ -28719,7 +28719,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S15" t="n">
-        <v>46.58924627590428</v>
+        <v>46.58924627590427</v>
       </c>
       <c r="T15" t="n">
         <v>134.5238485470482</v>
@@ -28734,7 +28734,7 @@
         <v>-518.8620467864769</v>
       </c>
       <c r="X15" t="n">
-        <v>504.3818749106284</v>
+        <v>504.3818749106283</v>
       </c>
       <c r="Y15" t="n">
         <v>1700.553410290818</v>
@@ -28746,7 +28746,7 @@
         <v>806.5780549321429</v>
       </c>
       <c r="AB15" t="n">
-        <v>403.5923498130973</v>
+        <v>403.5923498130974</v>
       </c>
       <c r="AC15" t="n">
         <v>1287.167022565553</v>
@@ -28832,7 +28832,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S16" t="n">
-        <v>46.89245212323169</v>
+        <v>46.89245212323168</v>
       </c>
       <c r="T16" t="n">
         <v>135.1700237543756</v>
@@ -28954,7 +28954,7 @@
         <v>750.7650883333333</v>
       </c>
       <c r="V17" t="n">
-        <v>928.2567708333333</v>
+        <v>928.2567708333335</v>
       </c>
       <c r="W17" t="n">
         <v>-518.8620467864769</v>
@@ -28972,7 +28972,7 @@
         <v>781.2405244107142</v>
       </c>
       <c r="AB17" t="n">
-        <v>381.0812227318887</v>
+        <v>381.0812227318888</v>
       </c>
       <c r="AC17" t="n">
         <v>1287.167022565553</v>
@@ -28990,7 +28990,7 @@
         <v>0.036599475</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01794433928571429</v>
+        <v>0.01794433928571428</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -28999,7 +28999,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.05454381428571429</v>
+        <v>0.05454381428571428</v>
       </c>
     </row>
     <row r="18">
@@ -29058,7 +29058,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S18" t="n">
-        <v>47.49886381788652</v>
+        <v>47.49886381788651</v>
       </c>
       <c r="T18" t="n">
         <v>136.4623741690304</v>
@@ -29067,13 +29067,13 @@
         <v>743.1022793333333</v>
       </c>
       <c r="V18" t="n">
-        <v>917.9137183333333</v>
+        <v>917.9137183333335</v>
       </c>
       <c r="W18" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X18" t="n">
-        <v>509.2033113921899</v>
+        <v>509.2033113921898</v>
       </c>
       <c r="Y18" t="n">
         <v>1651.35726227238</v>
@@ -29097,7 +29097,7 @@
         <v>609.7318513333332</v>
       </c>
       <c r="AF18" t="n">
-        <v>1447.969726831337</v>
+        <v>1447.969726831336</v>
       </c>
       <c r="AG18" t="n">
         <v>0.03600597</v>
@@ -29171,7 +29171,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S19" t="n">
-        <v>47.80206966521393</v>
+        <v>47.80206966521392</v>
       </c>
       <c r="T19" t="n">
         <v>137.1085493763578</v>
@@ -29180,7 +29180,7 @@
         <v>735.4394703333332</v>
       </c>
       <c r="V19" t="n">
-        <v>907.5706658333334</v>
+        <v>907.5706658333335</v>
       </c>
       <c r="W19" t="n">
         <v>-518.8620467864769</v>
@@ -29210,7 +29210,7 @@
         <v>615.1397843333333</v>
       </c>
       <c r="AF19" t="n">
-        <v>1466.95758540176</v>
+        <v>1466.957585401759</v>
       </c>
       <c r="AG19" t="n">
         <v>0.035412465</v>
@@ -29284,16 +29284,16 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S20" t="n">
-        <v>48.10527551254134</v>
+        <v>48.10527551254133</v>
       </c>
       <c r="T20" t="n">
-        <v>137.7547245836853</v>
+        <v>137.7547245836852</v>
       </c>
       <c r="U20" t="n">
         <v>727.7766613333332</v>
       </c>
       <c r="V20" t="n">
-        <v>897.2276133333334</v>
+        <v>897.2276133333335</v>
       </c>
       <c r="W20" t="n">
         <v>-518.8620467864769</v>
@@ -29397,7 +29397,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S21" t="n">
-        <v>48.40848135986875</v>
+        <v>48.40848135986874</v>
       </c>
       <c r="T21" t="n">
         <v>138.4008997910126</v>
@@ -29406,13 +29406,13 @@
         <v>720.1138523333333</v>
       </c>
       <c r="V21" t="n">
-        <v>886.8845608333334</v>
+        <v>886.8845608333335</v>
       </c>
       <c r="W21" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X21" t="n">
-        <v>514.0247478737514</v>
+        <v>514.0247478737513</v>
       </c>
       <c r="Y21" t="n">
         <v>1602.161114253941</v>
@@ -29442,7 +29442,7 @@
         <v>0.034225455</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.01678038214285715</v>
+        <v>0.01678038214285714</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -29451,7 +29451,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.05100583714285715</v>
+        <v>0.05100583714285714</v>
       </c>
     </row>
     <row r="22">
@@ -29519,13 +29519,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V22" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W22" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X22" t="n">
-        <v>515.6318933676052</v>
+        <v>515.6318933676051</v>
       </c>
       <c r="Y22" t="n">
         <v>1585.762398247795</v>
@@ -29537,7 +29537,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB22" t="n">
-        <v>324.8034050288671</v>
+        <v>324.8034050288672</v>
       </c>
       <c r="AC22" t="n">
         <v>1287.167022565553</v>
@@ -29623,7 +29623,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S23" t="n">
-        <v>49.01489305452358</v>
+        <v>49.01489305452357</v>
       </c>
       <c r="T23" t="n">
         <v>139.3502808456675</v>
@@ -29632,13 +29632,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V23" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W23" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X23" t="n">
-        <v>517.2390388614591</v>
+        <v>517.239038861459</v>
       </c>
       <c r="Y23" t="n">
         <v>1587.369543741649</v>
@@ -29736,7 +29736,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S24" t="n">
-        <v>49.31809890185099</v>
+        <v>49.31809890185098</v>
       </c>
       <c r="T24" t="n">
         <v>139.6534866929949</v>
@@ -29745,13 +29745,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V24" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W24" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X24" t="n">
-        <v>518.846184355313</v>
+        <v>518.8461843553129</v>
       </c>
       <c r="Y24" t="n">
         <v>1588.976689235503</v>
@@ -29763,7 +29763,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB24" t="n">
-        <v>302.2922779476585</v>
+        <v>302.2922779476586</v>
       </c>
       <c r="AC24" t="n">
         <v>1287.167022565553</v>
@@ -29849,7 +29849,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S25" t="n">
-        <v>49.6213047491784</v>
+        <v>49.62130474917839</v>
       </c>
       <c r="T25" t="n">
         <v>139.9566925403223</v>
@@ -29858,13 +29858,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V25" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W25" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X25" t="n">
-        <v>520.4533298491667</v>
+        <v>520.4533298491666</v>
       </c>
       <c r="Y25" t="n">
         <v>1590.583834729357</v>
@@ -29876,7 +29876,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB25" t="n">
-        <v>291.0367144070542</v>
+        <v>291.0367144070543</v>
       </c>
       <c r="AC25" t="n">
         <v>1287.167022565553</v>
@@ -29962,7 +29962,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S26" t="n">
-        <v>49.92451059650581</v>
+        <v>49.9245105965058</v>
       </c>
       <c r="T26" t="n">
         <v>140.2598983876497</v>
@@ -29971,13 +29971,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V26" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W26" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X26" t="n">
-        <v>522.0604753430206</v>
+        <v>522.0604753430205</v>
       </c>
       <c r="Y26" t="n">
         <v>1592.19098022321</v>
@@ -29989,7 +29989,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB26" t="n">
-        <v>279.7811508664499</v>
+        <v>279.78115086645</v>
       </c>
       <c r="AC26" t="n">
         <v>1287.167022565553</v>
@@ -30084,13 +30084,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V27" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W27" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X27" t="n">
-        <v>523.6676208368744</v>
+        <v>523.6676208368743</v>
       </c>
       <c r="Y27" t="n">
         <v>1593.798125717064</v>
@@ -30102,7 +30102,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB27" t="n">
-        <v>268.5255873258456</v>
+        <v>268.5255873258457</v>
       </c>
       <c r="AC27" t="n">
         <v>1287.167022565553</v>
@@ -30114,7 +30114,7 @@
         <v>631.3635833333333</v>
       </c>
       <c r="AF27" t="n">
-        <v>1618.860453965145</v>
+        <v>1618.860453965144</v>
       </c>
       <c r="AG27" t="n">
         <v>0.03363195</v>
@@ -30188,7 +30188,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S28" t="n">
-        <v>50.53092229116064</v>
+        <v>50.53092229116063</v>
       </c>
       <c r="T28" t="n">
         <v>140.8663100823045</v>
@@ -30197,13 +30197,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V28" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W28" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X28" t="n">
-        <v>525.2747663307283</v>
+        <v>525.2747663307282</v>
       </c>
       <c r="Y28" t="n">
         <v>1595.405271210918</v>
@@ -30227,7 +30227,7 @@
         <v>631.3635833333333</v>
       </c>
       <c r="AF28" t="n">
-        <v>1637.848312535568</v>
+        <v>1637.848312535567</v>
       </c>
       <c r="AG28" t="n">
         <v>0.03363195</v>
@@ -30301,22 +30301,22 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S29" t="n">
-        <v>50.83412813848805</v>
+        <v>50.83412813848804</v>
       </c>
       <c r="T29" t="n">
-        <v>141.169515929632</v>
+        <v>141.1695159296319</v>
       </c>
       <c r="U29" t="n">
         <v>712.4510433333332</v>
       </c>
       <c r="V29" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W29" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X29" t="n">
-        <v>526.8819118245822</v>
+        <v>526.8819118245821</v>
       </c>
       <c r="Y29" t="n">
         <v>1597.012416704772</v>
@@ -30414,7 +30414,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S30" t="n">
-        <v>51.13733398581546</v>
+        <v>51.13733398581545</v>
       </c>
       <c r="T30" t="n">
         <v>141.4727217769594</v>
@@ -30423,13 +30423,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V30" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W30" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X30" t="n">
-        <v>528.4890573184359</v>
+        <v>528.4890573184358</v>
       </c>
       <c r="Y30" t="n">
         <v>1598.619562198626</v>
@@ -30527,7 +30527,7 @@
         <v>64.50103819114391</v>
       </c>
       <c r="S31" t="n">
-        <v>51.44053983314287</v>
+        <v>51.44053983314286</v>
       </c>
       <c r="T31" t="n">
         <v>141.7759276242868</v>
@@ -30536,13 +30536,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V31" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W31" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X31" t="n">
-        <v>530.0962028122898</v>
+        <v>530.0962028122897</v>
       </c>
       <c r="Y31" t="n">
         <v>1600.22670769248</v>
@@ -30649,13 +30649,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V32" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W32" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X32" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y32" t="n">
         <v>1601.833853186333</v>
@@ -30762,13 +30762,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V33" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W33" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X33" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y33" t="n">
         <v>1601.833853186333</v>
@@ -30875,13 +30875,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V34" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W34" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X34" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y34" t="n">
         <v>1601.833853186333</v>
@@ -30988,13 +30988,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V35" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W35" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X35" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y35" t="n">
         <v>1601.833853186333</v>
@@ -31101,13 +31101,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V36" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W36" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X36" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y36" t="n">
         <v>1601.833853186333</v>
@@ -31119,7 +31119,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB36" t="n">
-        <v>202.7893128660137</v>
+        <v>202.7893128660138</v>
       </c>
       <c r="AC36" t="n">
         <v>1287.167022565553</v>
@@ -31214,13 +31214,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V37" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W37" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X37" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y37" t="n">
         <v>1601.833853186333</v>
@@ -31232,7 +31232,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB37" t="n">
-        <v>200.4246986768111</v>
+        <v>200.4246986768112</v>
       </c>
       <c r="AC37" t="n">
         <v>1287.167022565553</v>
@@ -31327,13 +31327,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V38" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W38" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X38" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y38" t="n">
         <v>1601.833853186333</v>
@@ -31440,13 +31440,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V39" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W39" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X39" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y39" t="n">
         <v>1601.833853186333</v>
@@ -31553,13 +31553,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V40" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W40" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X40" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y40" t="n">
         <v>1601.833853186333</v>
@@ -31666,13 +31666,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V41" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W41" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X41" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y41" t="n">
         <v>1601.833853186333</v>
@@ -31779,13 +31779,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V42" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W42" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X42" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y42" t="n">
         <v>1601.833853186333</v>
@@ -31892,13 +31892,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V43" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W43" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X43" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y43" t="n">
         <v>1601.833853186333</v>
@@ -31910,7 +31910,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB43" t="n">
-        <v>186.2370135415956</v>
+        <v>186.2370135415957</v>
       </c>
       <c r="AC43" t="n">
         <v>1287.167022565553</v>
@@ -32005,13 +32005,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V44" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W44" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X44" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y44" t="n">
         <v>1601.833853186333</v>
@@ -32023,7 +32023,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB44" t="n">
-        <v>183.872399352393</v>
+        <v>183.8723993523931</v>
       </c>
       <c r="AC44" t="n">
         <v>1287.167022565553</v>
@@ -32118,13 +32118,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V45" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W45" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X45" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y45" t="n">
         <v>1601.833853186333</v>
@@ -32231,13 +32231,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V46" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W46" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X46" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y46" t="n">
         <v>1601.833853186333</v>
@@ -32344,13 +32344,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V47" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W47" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X47" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y47" t="n">
         <v>1601.833853186333</v>
@@ -32457,13 +32457,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V48" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W48" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X48" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y48" t="n">
         <v>1601.833853186333</v>
@@ -32570,13 +32570,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V49" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W49" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X49" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y49" t="n">
         <v>1601.833853186333</v>
@@ -32683,13 +32683,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V50" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W50" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X50" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y50" t="n">
         <v>1601.833853186333</v>
@@ -32701,7 +32701,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB50" t="n">
-        <v>169.6847142171775</v>
+        <v>169.6847142171776</v>
       </c>
       <c r="AC50" t="n">
         <v>1287.167022565553</v>
@@ -32796,13 +32796,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V51" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W51" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X51" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y51" t="n">
         <v>1601.833853186333</v>
@@ -32814,7 +32814,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB51" t="n">
-        <v>167.3201000279749</v>
+        <v>167.320100027975</v>
       </c>
       <c r="AC51" t="n">
         <v>1287.167022565553</v>
@@ -32909,13 +32909,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V52" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W52" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X52" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y52" t="n">
         <v>1601.833853186333</v>
@@ -33022,13 +33022,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V53" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W53" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X53" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y53" t="n">
         <v>1601.833853186333</v>
@@ -33135,13 +33135,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V54" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W54" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X54" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y54" t="n">
         <v>1601.833853186333</v>
@@ -33248,13 +33248,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V55" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W55" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X55" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y55" t="n">
         <v>1601.833853186333</v>
@@ -33361,13 +33361,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V56" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W56" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X56" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y56" t="n">
         <v>1601.833853186333</v>
@@ -33474,13 +33474,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V57" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W57" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X57" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y57" t="n">
         <v>1601.833853186333</v>
@@ -33492,7 +33492,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB57" t="n">
-        <v>153.1324148927594</v>
+        <v>153.1324148927595</v>
       </c>
       <c r="AC57" t="n">
         <v>1287.167022565553</v>
@@ -33587,13 +33587,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V58" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W58" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X58" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y58" t="n">
         <v>1601.833853186333</v>
@@ -33605,7 +33605,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB58" t="n">
-        <v>150.7678007035568</v>
+        <v>150.7678007035569</v>
       </c>
       <c r="AC58" t="n">
         <v>1287.167022565553</v>
@@ -33700,13 +33700,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V59" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W59" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X59" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y59" t="n">
         <v>1601.833853186333</v>
@@ -33813,13 +33813,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V60" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W60" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X60" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y60" t="n">
         <v>1601.833853186333</v>
@@ -33926,13 +33926,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V61" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W61" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X61" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y61" t="n">
         <v>1601.833853186333</v>
@@ -34039,13 +34039,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V62" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W62" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X62" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y62" t="n">
         <v>1601.833853186333</v>
@@ -34152,13 +34152,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V63" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W63" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X63" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y63" t="n">
         <v>1601.833853186333</v>
@@ -34265,13 +34265,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V64" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W64" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X64" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y64" t="n">
         <v>1601.833853186333</v>
@@ -34378,13 +34378,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V65" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W65" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X65" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y65" t="n">
         <v>1601.833853186333</v>
@@ -34491,13 +34491,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V66" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W66" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X66" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y66" t="n">
         <v>1601.833853186333</v>
@@ -34604,13 +34604,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V67" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W67" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X67" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y67" t="n">
         <v>1601.833853186333</v>
@@ -34717,13 +34717,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V68" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W68" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X68" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y68" t="n">
         <v>1601.833853186333</v>
@@ -34830,13 +34830,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V69" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W69" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X69" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y69" t="n">
         <v>1601.833853186333</v>
@@ -34943,13 +34943,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V70" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W70" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X70" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y70" t="n">
         <v>1601.833853186333</v>
@@ -35056,13 +35056,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V71" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W71" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X71" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y71" t="n">
         <v>1601.833853186333</v>
@@ -35169,13 +35169,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V72" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W72" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X72" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y72" t="n">
         <v>1601.833853186333</v>
@@ -35282,13 +35282,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V73" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W73" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X73" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y73" t="n">
         <v>1601.833853186333</v>
@@ -35395,13 +35395,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V74" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W74" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X74" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y74" t="n">
         <v>1601.833853186333</v>
@@ -35508,13 +35508,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V75" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W75" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X75" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y75" t="n">
         <v>1601.833853186333</v>
@@ -35621,13 +35621,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V76" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W76" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X76" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y76" t="n">
         <v>1601.833853186333</v>
@@ -35734,13 +35734,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V77" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W77" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X77" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y77" t="n">
         <v>1601.833853186333</v>
@@ -35847,13 +35847,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V78" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W78" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X78" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y78" t="n">
         <v>1601.833853186333</v>
@@ -35960,13 +35960,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V79" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W79" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X79" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y79" t="n">
         <v>1601.833853186333</v>
@@ -36073,13 +36073,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V80" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W80" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X80" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y80" t="n">
         <v>1601.833853186333</v>
@@ -36091,7 +36091,7 @@
         <v>717.8966981071428</v>
       </c>
       <c r="AB80" t="n">
-        <v>123.8584912304314</v>
+        <v>123.8584912304315</v>
       </c>
       <c r="AC80" t="n">
         <v>1287.167022565553</v>
@@ -36186,13 +36186,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V81" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W81" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X81" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y81" t="n">
         <v>1601.833853186333</v>
@@ -36299,13 +36299,13 @@
         <v>712.4510433333332</v>
       </c>
       <c r="V82" t="n">
-        <v>876.5415083333334</v>
+        <v>876.5415083333335</v>
       </c>
       <c r="W82" t="n">
         <v>-518.8620467864769</v>
       </c>
       <c r="X82" t="n">
-        <v>531.7033483061437</v>
+        <v>531.7033483061435</v>
       </c>
       <c r="Y82" t="n">
         <v>1601.833853186333</v>
